--- a/artfynd/A 28682-2024 artfynd.xlsx
+++ b/artfynd/A 28682-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903852</v>
+        <v>110746831</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>57552</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eningen, Vg</t>
+          <t>Blommaskog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364242.1804926263</v>
+        <v>364223.9535124111</v>
       </c>
       <c r="R2" t="n">
-        <v>6394484.072847377</v>
+        <v>6394500.206555721</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -769,143 +778,22 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>110746831</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57552</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>208245</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Blommaskog, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>364223.9535124111</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6394500.206555721</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Borås</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Seglora</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Johan Svedholm</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Johan Svedholm</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28682-2024 artfynd.xlsx
+++ b/artfynd/A 28682-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110746831</v>
+        <v>90903852</v>
       </c>
       <c r="B2" t="n">
-        <v>57552</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blommaskog, Vg</t>
+          <t>Eningen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364223.9535124111</v>
+        <v>364242.1804926263</v>
       </c>
       <c r="R2" t="n">
-        <v>6394500.206555721</v>
+        <v>6394484.072847377</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -778,22 +769,143 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>110746831</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57552</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blommaskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364223.9535124111</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6394500.206555721</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Johan Svedholm</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Johan Svedholm</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28682-2024 artfynd.xlsx
+++ b/artfynd/A 28682-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903852</v>
+        <v>110746831</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eningen, Vg</t>
+          <t>Blommaskog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364242.1804926263</v>
+        <v>364224</v>
       </c>
       <c r="R2" t="n">
-        <v>6394484.072847377</v>
+        <v>6394500</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +763,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110746831</v>
+        <v>90903852</v>
       </c>
       <c r="B3" t="n">
-        <v>57552</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,46 +793,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blommaskog, Vg</t>
+          <t>Eningen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364223.9535124111</v>
+        <v>364242</v>
       </c>
       <c r="R3" t="n">
-        <v>6394500.206555721</v>
+        <v>6394484</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,22 +857,123 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110746846</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Eningsbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>364278</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6394478</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Johan Svedholm</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Johan Svedholm</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
